--- a/final_data_pipeline/output/325120longform.xlsx
+++ b/final_data_pipeline/output/325120longform.xlsx
@@ -3675,7 +3675,7 @@
         <v>136</v>
       </c>
       <c r="AA32">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB32">
         <v>8000</v>
@@ -3767,7 +3767,7 @@
         <v>136</v>
       </c>
       <c r="AA33">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB33">
         <v>8000</v>
@@ -3856,7 +3856,7 @@
         <v>136</v>
       </c>
       <c r="AA34">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB34">
         <v>8000</v>
@@ -6105,7 +6105,7 @@
         <v>136</v>
       </c>
       <c r="AA59">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AB59">
         <v>8000</v>
@@ -6194,7 +6194,7 @@
         <v>136</v>
       </c>
       <c r="AA60">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AB60">
         <v>8000</v>
@@ -6286,7 +6286,7 @@
         <v>136</v>
       </c>
       <c r="AA61">
-        <v>10</v>
+        <v>12.41429539295394</v>
       </c>
       <c r="AB61">
         <v>8000</v>
@@ -6375,7 +6375,7 @@
         <v>136</v>
       </c>
       <c r="AA62">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB62">
         <v>8000</v>
@@ -6464,7 +6464,7 @@
         <v>136</v>
       </c>
       <c r="AA63">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB63">
         <v>8000</v>
@@ -6553,7 +6553,7 @@
         <v>136</v>
       </c>
       <c r="AA64">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB64">
         <v>8000</v>
@@ -6642,7 +6642,7 @@
         <v>136</v>
       </c>
       <c r="AA65">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB65">
         <v>8000</v>
@@ -6734,7 +6734,7 @@
         <v>136</v>
       </c>
       <c r="AA66">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB66">
         <v>8000</v>
@@ -6826,7 +6826,7 @@
         <v>136</v>
       </c>
       <c r="AA67">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB67">
         <v>8000</v>
@@ -7185,7 +7185,7 @@
         <v>136</v>
       </c>
       <c r="AA71">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AB71">
         <v>8000</v>
@@ -7274,7 +7274,7 @@
         <v>136</v>
       </c>
       <c r="AA72">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AB72">
         <v>8000</v>
@@ -7366,7 +7366,7 @@
         <v>136</v>
       </c>
       <c r="AA73">
-        <v>10</v>
+        <v>21.79166666666666</v>
       </c>
       <c r="AB73">
         <v>8000</v>
@@ -7458,7 +7458,7 @@
         <v>136</v>
       </c>
       <c r="AA74">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB74">
         <v>8000</v>
@@ -7547,7 +7547,7 @@
         <v>136</v>
       </c>
       <c r="AA75">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB75">
         <v>8000</v>
@@ -7636,7 +7636,7 @@
         <v>136</v>
       </c>
       <c r="AA76">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB76">
         <v>8000</v>
@@ -11238,7 +11238,7 @@
         <v>136</v>
       </c>
       <c r="AA116">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AB116">
         <v>8000</v>
@@ -11327,7 +11327,7 @@
         <v>136</v>
       </c>
       <c r="AA117">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AB117">
         <v>8000</v>
@@ -11416,7 +11416,7 @@
         <v>136</v>
       </c>
       <c r="AA118">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AB118">
         <v>8000</v>
@@ -12045,7 +12045,7 @@
         <v>136</v>
       </c>
       <c r="AA125">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB125">
         <v>8000</v>
@@ -12134,7 +12134,7 @@
         <v>136</v>
       </c>
       <c r="AA126">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB126">
         <v>8000</v>
@@ -12226,7 +12226,7 @@
         <v>136</v>
       </c>
       <c r="AA127">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AB127">
         <v>8000</v>
@@ -12318,7 +12318,7 @@
         <v>136</v>
       </c>
       <c r="AA128">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="AB128">
         <v>8000</v>
@@ -12407,7 +12407,7 @@
         <v>136</v>
       </c>
       <c r="AA129">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="AB129">
         <v>8000</v>
@@ -12496,7 +12496,7 @@
         <v>136</v>
       </c>
       <c r="AA130">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="AB130">
         <v>8000</v>
@@ -12585,7 +12585,7 @@
         <v>136</v>
       </c>
       <c r="AA131">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB131">
         <v>8000</v>
@@ -12677,7 +12677,7 @@
         <v>136</v>
       </c>
       <c r="AA132">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB132">
         <v>8000</v>
@@ -12766,7 +12766,7 @@
         <v>136</v>
       </c>
       <c r="AA133">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB133">
         <v>8000</v>
